--- a/output/pdf_financials_xlsx/IPT.xlsx
+++ b/output/pdf_financials_xlsx/IPT.xlsx
@@ -8129,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-2880.532</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>555.889</v>
@@ -37182,7 +37182,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IPT.xlsx
+++ b/output/pdf_financials_xlsx/IPT.xlsx
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.01079</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>211.575</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>223.159</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.470779</v>
+        <v>5.459989</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>11.72549</v>
+        <v>-199.84951</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-263.996</v>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6.502965</v>
+        <v>6.492175</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1255.48749</v>
+        <v>1043.91249</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>1319.81</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>38.9919539313251</v>
+        <v>38.92725679964455</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5.17369654926867</v>
+        <v>4.301824184047796</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>8.282948601925687</v>
@@ -2691,52 +2691,52 @@
         <v>5.294881</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.294881</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>30775.25</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>16013.245</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.48518</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>575.3440000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>717.369</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>8.124563</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.71358</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.234427</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.773062</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>20.385551</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>21.081575</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>15.251161</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>15.251161</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>7.062715</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>23.699168</v>
       </c>
     </row>
     <row r="35">
@@ -2813,52 +2813,52 @@
         <v>5.294881</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>5.294881</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>30775.25</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>16013.245</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.48518</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>575.3440000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>717.369</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>8.124563</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>4.71358</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.234427</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.773062</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>20.385551</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>21.081575</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>15.251161</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>15.251161</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>7.062715</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>23.699168</v>
       </c>
     </row>
     <row r="37">
@@ -3551,19 +3551,19 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>16884.06</v>
+        <v>870.8150000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.62469</v>
+        <v>0.13951</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>592.8440000000001</v>
+        <v>17.5</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>722.369</v>
+        <v>5</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>12927.448061</v>
+        <v>12919.323498</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -58370,7 +58370,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">

--- a/output/pdf_financials_xlsx/IPT.xlsx
+++ b/output/pdf_financials_xlsx/IPT.xlsx
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>0</v>
+        <v>0.650778</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0</v>
+        <v>0.919808</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>0.919808</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.262412</v>
+        <v>2.611634</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.336628</v>
+        <v>1.41682</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.760054</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.27456</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0.27456</v>
@@ -22674,7 +22674,11 @@
           <t>Inventories Note 4</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>0.650778</v>
       </c>
@@ -23202,7 +23206,11 @@
           <t>Due to related party Note 7</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>0.760054</v>
       </c>

--- a/output/pdf_financials_xlsx/IPT.xlsx
+++ b/output/pdf_financials_xlsx/IPT.xlsx
@@ -599,7 +599,7 @@
         <v>14637.592</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>16684.658</v>
+        <v>16.684658</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>15.364726</v>
@@ -607,20 +607,14 @@
       <c r="L4" s="3" t="n">
         <v>13.098339</v>
       </c>
-      <c r="M4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M4" s="3" t="n">
+        <v>13.311376</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>15.577843</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>17.699122</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>16.335788</v>
@@ -678,20 +672,14 @@
       <c r="L5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
@@ -741,7 +729,7 @@
         <v>14637.592</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>16684.658</v>
+        <v>16.684658</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>15.364726</v>
@@ -749,20 +737,14 @@
       <c r="L6" s="3" t="n">
         <v>13.098339</v>
       </c>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M6" s="3" t="n">
+        <v>13.311376</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15.577843</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17.699122</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>16.335788</v>
@@ -820,20 +802,14 @@
       <c r="L7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0</v>
@@ -891,20 +867,14 @@
       <c r="L8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
@@ -962,20 +932,14 @@
       <c r="L9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0</v>
@@ -1025,7 +989,7 @@
         <v>12630.791</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>12984.236</v>
+        <v>12.984236</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>14.894005</v>
@@ -1033,20 +997,14 @@
       <c r="L10" s="3" t="n">
         <v>14.777527</v>
       </c>
-      <c r="M10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M10" s="3" t="n">
+        <v>11.946199</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>10.899394</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>12.971946</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>15.114777</v>
@@ -1096,7 +1054,7 @@
         <v>-1666.3</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1130.81</v>
+        <v>-1.13081</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-3.937734</v>
@@ -1104,20 +1062,14 @@
       <c r="L11" s="3" t="n">
         <v>-4.837911</v>
       </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M11" s="3" t="n">
+        <v>-2.270887</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>1.258543</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0.211795</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>-2.611497</v>
@@ -1167,7 +1119,7 @@
         <v>133.261</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>31.843</v>
+        <v>0.031843</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0.052247</v>
@@ -1175,20 +1127,14 @@
       <c r="L12" s="3" t="n">
         <v>0.028782</v>
       </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M12" s="3" t="n">
+        <v>0.038287</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0.064149</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0.206157</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.265407</v>
@@ -1246,20 +1192,14 @@
       <c r="L13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>-0</v>
@@ -1317,20 +1257,14 @@
       <c r="L14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0</v>
@@ -1380,28 +1314,22 @@
         <v>473.56</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-428.814</v>
+        <v>-0.428814</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>-0.561406</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>-0.228335</v>
-      </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.233634</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>-0.221349</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>-0.183335</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>-0.05225</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.047985</v>
@@ -1451,7 +1379,7 @@
         <v>-1305.581</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1804.793</v>
+        <v>-1.804793</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-4.620176</v>
@@ -1459,23 +1387,17 @@
       <c r="L16" s="3" t="n">
         <v>-5.062651</v>
       </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M16" s="3" t="n">
+        <v>-4.921773</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1.100318</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0.276116</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-3.134387</v>
+        <v>-2.589458</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>-7.557123</v>
@@ -1522,7 +1444,7 @@
         <v>-122.257</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-134.485</v>
+        <v>-0.134485</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0.015521</v>
@@ -1530,20 +1452,14 @@
       <c r="L17" s="3" t="n">
         <v>-0.000281</v>
       </c>
-      <c r="M17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M17" s="3" t="n">
+        <v>-0.017649</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>-0.20074</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>-0.173209</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0.0284</v>
@@ -1787,7 +1703,7 @@
         <v>-1427.838</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-1939.278</v>
+        <v>-1.939278</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-4.635697</v>
@@ -1795,20 +1711,14 @@
       <c r="L20" s="3" t="n">
         <v>-5.062932</v>
       </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M20" s="3" t="n">
+        <v>-4.939422</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>2.301012</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>-0.545335</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>-3.162787</v>
@@ -1866,20 +1776,14 @@
       <c r="L21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -1937,20 +1841,14 @@
       <c r="L22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
@@ -2000,7 +1898,7 @@
         <v>-1427.838</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-1939.278</v>
+        <v>-1.939278</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-4.635697</v>
@@ -2011,10 +1909,8 @@
       <c r="M23" s="3" t="n">
         <v>-4.939422</v>
       </c>
-      <c r="N23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" s="3" t="n">
+        <v>2.301012</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-0.545335</v>
@@ -2075,20 +1971,14 @@
       <c r="L24" s="3" t="n">
         <v>-0.06</v>
       </c>
-      <c r="M24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M24" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>-0.02</v>
@@ -2146,20 +2036,14 @@
       <c r="L25" s="3" t="n">
         <v>-0.06</v>
       </c>
-      <c r="M25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M25" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>-0.02</v>
@@ -2209,7 +2093,7 @@
         <v>71391.89999999999</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>96963.89999999999</v>
+        <v>96.9639</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>92.71393999999999</v>
@@ -2217,20 +2101,14 @@
       <c r="L26" s="3" t="n">
         <v>84.3822</v>
       </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M26" s="3" t="n">
+        <v>98.78843999999999</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>131.913313</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>144.617071</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>158.13935</v>
@@ -2280,7 +2158,7 @@
         <v>-1438.842</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1836.636</v>
+        <v>-1.836636</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-4.672423</v>
@@ -2288,23 +2166,17 @@
       <c r="L27" s="3" t="n">
         <v>-5.091433</v>
       </c>
-      <c r="M27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M27" s="3" t="n">
+        <v>-4.96006</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>1.036169</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0.06995899999999999</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.399794</v>
+        <v>-2.854865</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-8.037544</v>
@@ -2351,7 +2223,7 @@
         <v>2107.807</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2331.822</v>
+        <v>2.331822</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>2.211739</v>
@@ -2359,20 +2231,14 @@
       <c r="L28" s="3" t="n">
         <v>1.864915</v>
       </c>
-      <c r="M28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M28" s="3" t="n">
+        <v>1.541203</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>1.429145</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>1.301335</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>1.389993</v>
@@ -2422,7 +2288,7 @@
         <v>668.965</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>495.186</v>
+        <v>0.495186</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-2.460684</v>
@@ -2430,23 +2296,17 @@
       <c r="L29" s="3" t="n">
         <v>-3.226518</v>
       </c>
-      <c r="M29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M29" s="3" t="n">
+        <v>-3.418857</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>2.465314</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>1.371294</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.009801</v>
+        <v>-1.464872</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-6.222253</v>
@@ -2501,23 +2361,17 @@
       <c r="L30" s="3" t="n">
         <v>-24.63303171493729</v>
       </c>
-      <c r="M30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M30" s="3" t="n">
+        <v>-25.68372345578699</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>15.82577254116632</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>7.747808055111434</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-12.30305510820782</v>
+        <v>-8.967256431094722</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>-29.96995804858134</v>
@@ -2572,23 +2426,17 @@
       <c r="L31" s="3" t="n">
         <v>-0.005550451729736061</v>
       </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M31" s="3" t="n">
+        <v>-0.3585902884996931</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>18.24381678751052</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>62.73051905720784</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.9060782858019766</v>
+        <v>-1.096754610424266</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>-0.107461530002886</v>
@@ -2643,20 +2491,14 @@
       <c r="L32" s="3" t="n">
         <v>-38.6532368722477</v>
       </c>
-      <c r="M32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M32" s="3" t="n">
+        <v>-37.1067724328424</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>14.77105655770186</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>-3.081141539111375</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>-19.36109234522387</v>
@@ -6909,10 +6751,8 @@
       <c r="M99" s="3" t="n">
         <v>-4.939422</v>
       </c>
-      <c r="N99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N99" s="3" t="n">
+        <v>2.301012</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>-0.545335</v>
@@ -7447,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="S107" s="3" t="n">
-        <v>0</v>
+        <v>1.226296</v>
       </c>
     </row>
     <row r="108">
@@ -7606,43 +7446,43 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.040196</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>23.739</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>28.935</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.038623</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.034904</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.030139</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.02945</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.029609</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.042909</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.053268</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.075805</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.176342</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.216669</v>
       </c>
     </row>
     <row r="111">
@@ -7946,7 +7786,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.527937</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -9341,7 +9181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V493"/>
+  <dimension ref="A1:V515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27238,7 +27078,11 @@
           <t>Share based compensation expense</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -27652,7 +27496,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -30720,7 +30568,11 @@
           <t>Accretion expense 176,342</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -33362,7 +33214,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -34854,7 +34710,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -35058,7 +34918,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -35556,7 +35420,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -44646,7 +44514,7 @@
         <v>14738.598</v>
       </c>
       <c r="M342" s="5" t="n">
-        <v>15316.058</v>
+        <v>15.316058</v>
       </c>
       <c r="N342" s="5" t="n">
         <v>17.105744</v>
@@ -44654,20 +44522,14 @@
       <c r="O342" s="5" t="n">
         <v>16.642442</v>
       </c>
-      <c r="P342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P342" s="5" t="n">
+        <v>13.487402</v>
+      </c>
+      <c r="Q342" s="5" t="n">
+        <v>12.328539</v>
+      </c>
+      <c r="R342" s="5" t="n">
+        <v>14.273281</v>
       </c>
       <c r="S342" s="5" t="n">
         <v>16.50477</v>
@@ -48990,7 +48852,7 @@
         <v>14637.592</v>
       </c>
       <c r="M383" s="5" t="n">
-        <v>16684.658</v>
+        <v>16.684658</v>
       </c>
       <c r="N383" s="5" t="n">
         <v>15.364726</v>
@@ -49003,15 +48865,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q383" s="5" t="n">
+        <v>15.577843</v>
+      </c>
+      <c r="R383" s="5" t="n">
+        <v>17.699122</v>
       </c>
       <c r="S383" s="5" t="n">
         <v>16.335788</v>
@@ -49101,15 +48959,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O384" s="5" t="n">
+        <v>14.777527</v>
+      </c>
+      <c r="P384" s="5" t="n">
+        <v>11.946199</v>
       </c>
       <c r="Q384" t="inlineStr">
         <is>
@@ -49188,7 +49042,7 @@
         <v>2107.807</v>
       </c>
       <c r="M385" s="5" t="n">
-        <v>2331.822</v>
+        <v>2.331822</v>
       </c>
       <c r="N385" s="5" t="n">
         <v>2.211739</v>
@@ -49196,20 +49050,14 @@
       <c r="O385" s="5" t="n">
         <v>1.864915</v>
       </c>
-      <c r="P385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P385" s="5" t="n">
+        <v>1.541203</v>
+      </c>
+      <c r="Q385" s="5" t="n">
+        <v>1.429145</v>
+      </c>
+      <c r="R385" s="5" t="n">
+        <v>1.301335</v>
       </c>
       <c r="S385" s="5" t="n">
         <v>1.389993</v>
@@ -49296,10 +49144,8 @@
       <c r="O386" s="5" t="n">
         <v>-3.544103</v>
       </c>
-      <c r="P386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P386" s="5" t="n">
+        <v>-0.176026</v>
       </c>
       <c r="Q386" t="inlineStr">
         <is>
@@ -49374,7 +49220,7 @@
         <v>221.497</v>
       </c>
       <c r="M387" s="5" t="n">
-        <v>187.853</v>
+        <v>0.187853</v>
       </c>
       <c r="N387" s="5" t="n">
         <v>0.184581</v>
@@ -49382,20 +49228,14 @@
       <c r="O387" s="5" t="n">
         <v>0.160534</v>
       </c>
-      <c r="P387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P387" s="5" t="n">
+        <v>0.161222</v>
+      </c>
+      <c r="Q387" s="5" t="n">
+        <v>0.209117</v>
+      </c>
+      <c r="R387" s="5" t="n">
+        <v>0.224311</v>
       </c>
       <c r="S387" s="5" t="n">
         <v>0.173071</v>
@@ -49464,7 +49304,7 @@
         <v>31.793</v>
       </c>
       <c r="M388" s="5" t="n">
-        <v>29.02</v>
+        <v>0.02902</v>
       </c>
       <c r="N388" s="5" t="n">
         <v>0.02415</v>
@@ -49472,20 +49312,14 @@
       <c r="O388" s="5" t="n">
         <v>0.017536</v>
       </c>
-      <c r="P388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P388" s="5" t="n">
+        <v>0.018881</v>
+      </c>
+      <c r="Q388" s="5" t="n">
+        <v>0.033029</v>
+      </c>
+      <c r="R388" s="5" t="n">
+        <v>0.04088</v>
       </c>
       <c r="S388" s="5" t="n">
         <v>0.020273</v>
@@ -49550,7 +49384,7 @@
         <v>35.962</v>
       </c>
       <c r="M389" s="5" t="n">
-        <v>69.494</v>
+        <v>0.069494</v>
       </c>
       <c r="N389" s="5" t="n">
         <v>0.0696</v>
@@ -49558,20 +49392,14 @@
       <c r="O389" s="5" t="n">
         <v>0.062517</v>
       </c>
-      <c r="P389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P389" s="5" t="n">
+        <v>0.408423</v>
+      </c>
+      <c r="Q389" s="5" t="n">
+        <v>0.416363</v>
+      </c>
+      <c r="R389" s="5" t="n">
+        <v>0.072768</v>
       </c>
       <c r="S389" s="5" t="n">
         <v>0.111313</v>
@@ -49636,7 +49464,7 @@
         <v>341.788</v>
       </c>
       <c r="M390" s="5" t="n">
-        <v>351.74</v>
+        <v>0.35174</v>
       </c>
       <c r="N390" s="5" t="n">
         <v>0.215226</v>
@@ -49644,20 +49472,14 @@
       <c r="O390" s="5" t="n">
         <v>0.178568</v>
       </c>
-      <c r="P390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P390" s="5" t="n">
+        <v>0.22926</v>
+      </c>
+      <c r="Q390" s="5" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="R390" s="5" t="n">
+        <v>0.316226</v>
       </c>
       <c r="S390" s="5" t="n">
         <v>0.702877</v>
@@ -49722,7 +49544,7 @@
         <v>306.981</v>
       </c>
       <c r="M391" s="5" t="n">
-        <v>277.39</v>
+        <v>0.27739</v>
       </c>
       <c r="N391" s="5" t="n">
         <v>0.281089</v>
@@ -49730,20 +49552,14 @@
       <c r="O391" s="5" t="n">
         <v>0.249126</v>
       </c>
-      <c r="P391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P391" s="5" t="n">
+        <v>0.273316</v>
+      </c>
+      <c r="Q391" s="5" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="R391" s="5" t="n">
+        <v>0.344475</v>
       </c>
       <c r="S391" s="5" t="n">
         <v>0.379884</v>
@@ -49808,7 +49624,7 @@
         <v>627.273</v>
       </c>
       <c r="M392" s="5" t="n">
-        <v>836.4690000000001</v>
+        <v>0.836469</v>
       </c>
       <c r="N392" s="5" t="n">
         <v>0.686608</v>
@@ -49816,20 +49632,14 @@
       <c r="O392" s="5" t="n">
         <v>0.6439859999999999</v>
       </c>
-      <c r="P392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P392" s="5" t="n">
+        <v>0.5896980000000001</v>
+      </c>
+      <c r="Q392" s="5" t="n">
+        <v>0.6433219999999999</v>
+      </c>
+      <c r="R392" s="5" t="n">
+        <v>0.743661</v>
       </c>
       <c r="S392" s="5" t="n">
         <v>1.055097</v>
@@ -49898,7 +49708,7 @@
         <v>1565.294</v>
       </c>
       <c r="M393" s="5" t="n">
-        <v>2499.41</v>
+        <v>2.49941</v>
       </c>
       <c r="N393" s="5" t="n">
         <v>2.196716</v>
@@ -49906,20 +49716,14 @@
       <c r="O393" s="5" t="n">
         <v>1.293808</v>
       </c>
-      <c r="P393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P393" s="5" t="n">
+        <v>2.094861</v>
+      </c>
+      <c r="Q393" s="5" t="n">
+        <v>1.990761</v>
+      </c>
+      <c r="R393" s="5" t="n">
+        <v>3.214046</v>
       </c>
       <c r="S393" s="5" t="n">
         <v>2.442515</v>
@@ -49994,7 +49798,7 @@
         <v>-1666.3</v>
       </c>
       <c r="M394" s="5" t="n">
-        <v>-1130.81</v>
+        <v>-1.13081</v>
       </c>
       <c r="N394" s="5" t="n">
         <v>-3.937734</v>
@@ -50002,10 +49806,8 @@
       <c r="O394" s="5" t="n">
         <v>-4.837911</v>
       </c>
-      <c r="P394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P394" s="5" t="n">
+        <v>-2.270887</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -50086,7 +49888,7 @@
         <v>-55.522</v>
       </c>
       <c r="M395" s="5" t="n">
-        <v>-60.144</v>
+        <v>-0.060144</v>
       </c>
       <c r="N395" s="5" t="n">
         <v>-0.034904</v>
@@ -50094,20 +49896,14 @@
       <c r="O395" s="5" t="n">
         <v>-0.030139</v>
       </c>
-      <c r="P395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P395" s="5" t="n">
+        <v>-0.035345</v>
+      </c>
+      <c r="Q395" s="5" t="n">
+        <v>-0.037182</v>
+      </c>
+      <c r="R395" s="5" t="n">
+        <v>-0.056135</v>
       </c>
       <c r="S395" s="5" t="n">
         <v>-0.069171</v>
@@ -50182,7 +49978,7 @@
         <v>133.261</v>
       </c>
       <c r="M396" s="5" t="n">
-        <v>31.843</v>
+        <v>0.031843</v>
       </c>
       <c r="N396" s="5" t="n">
         <v>0.052247</v>
@@ -50190,20 +49986,14 @@
       <c r="O396" s="5" t="n">
         <v>0.028782</v>
       </c>
-      <c r="P396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P396" s="5" t="n">
+        <v>0.038287</v>
+      </c>
+      <c r="Q396" s="5" t="n">
+        <v>0.064149</v>
+      </c>
+      <c r="R396" s="5" t="n">
+        <v>0.206157</v>
       </c>
       <c r="S396" s="5" t="n">
         <v>0.265407</v>
@@ -50378,12 +50168,10 @@
         <v>410.704</v>
       </c>
       <c r="M398" s="5" t="n">
-        <v>69.697</v>
-      </c>
-      <c r="N398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.069697</v>
+      </c>
+      <c r="N398" s="5" t="n">
+        <v>0.068939</v>
       </c>
       <c r="O398" t="inlineStr">
         <is>
@@ -50395,15 +50183,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q398" s="5" t="n">
+        <v>0.058529</v>
+      </c>
+      <c r="R398" s="5" t="n">
+        <v>0.035445</v>
       </c>
       <c r="S398" s="5" t="n">
         <v>0.055854</v>
@@ -50598,10 +50382,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P400" s="5" t="n">
+        <v>-2.32134</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -50682,7 +50464,7 @@
         <v>7.055</v>
       </c>
       <c r="M401" s="5" t="n">
-        <v>513.385</v>
+        <v>0.513385</v>
       </c>
       <c r="N401" s="5" t="n">
         <v>0.157432</v>
@@ -50690,20 +50472,14 @@
       <c r="O401" s="5" t="n">
         <v>0.234991</v>
       </c>
-      <c r="P401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P401" s="5" t="n">
+        <v>3.070904</v>
+      </c>
+      <c r="Q401" s="5" t="n">
+        <v>0.158225</v>
+      </c>
+      <c r="R401" s="5" t="n">
+        <v>0.064321</v>
       </c>
       <c r="S401" s="5" t="n">
         <v>0.022039</v>
@@ -50772,7 +50548,7 @@
         <v>-1659.245</v>
       </c>
       <c r="M402" s="5" t="n">
-        <v>-1644.195</v>
+        <v>-1.644195</v>
       </c>
       <c r="N402" s="5" t="n">
         <v>-4.095166</v>
@@ -50780,10 +50556,8 @@
       <c r="O402" s="5" t="n">
         <v>-5.072902</v>
       </c>
-      <c r="P402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P402" s="5" t="n">
+        <v>-5.341791</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -51082,7 +50856,7 @@
         <v>-1427.838</v>
       </c>
       <c r="M405" s="5" t="n">
-        <v>-1939.278</v>
+        <v>-1.939278</v>
       </c>
       <c r="N405" s="5" t="n">
         <v>-4.635697</v>
@@ -51090,20 +50864,16 @@
       <c r="O405" s="5" t="n">
         <v>-5.062932</v>
       </c>
-      <c r="P405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P405" s="5" t="n">
+        <v>-4.939422</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R405" s="5" t="n">
+        <v>-0.545335</v>
       </c>
       <c r="S405" s="5" t="n">
         <v>-3.162787</v>
@@ -51312,10 +51082,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R407" s="5" t="n">
+        <v>144.617071</v>
       </c>
       <c r="S407" s="5" t="n">
         <v>147.277171</v>
@@ -51347,7 +51115,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Operating expenses (Note 11)</t>
+          <t>Operating expenses (Note 12)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -51370,21 +51138,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H408" s="5" t="n">
-        <v>10125.634</v>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I408" s="5" t="n">
         <v>10314.273</v>
       </c>
-      <c r="J408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J408" s="5" t="n">
+        <v>11.717504</v>
+      </c>
+      <c r="K408" s="5" t="n">
+        <v>12.034223</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -51396,31 +51162,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N408" s="5" t="n">
-        <v>14.894005</v>
-      </c>
-      <c r="O408" s="5" t="n">
-        <v>14.777527</v>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P408" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q408" s="5" t="n">
+        <v>10.899394</v>
+      </c>
+      <c r="R408" s="5" t="n">
+        <v>12.971946</v>
+      </c>
+      <c r="S408" s="5" t="n">
+        <v>15.114777</v>
       </c>
       <c r="T408" t="inlineStr">
         <is>
@@ -51446,12 +51210,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 13(b))</t>
+          <t>Mine operating (loss) income</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -51500,11 +51264,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N409" s="5" t="n">
-        <v>0.7354619999999999</v>
-      </c>
-      <c r="O409" s="5" t="n">
-        <v>-0.018459</v>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P409" t="inlineStr">
         <is>
@@ -51516,15 +51284,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R409" s="5" t="n">
+        <v>3.425841</v>
+      </c>
+      <c r="S409" s="5" t="n">
+        <v>-0.168982</v>
       </c>
       <c r="T409" t="inlineStr">
         <is>
@@ -51550,19 +51314,15 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share-based payments (Note 13(b))</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -51583,14 +51343,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I410" s="5" t="n">
-        <v>-381.623</v>
-      </c>
-      <c r="J410" s="5" t="n">
-        <v>-0.108842</v>
-      </c>
-      <c r="K410" s="5" t="n">
-        <v>-0.378725</v>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -51603,10 +51369,10 @@
         </is>
       </c>
       <c r="N410" s="5" t="n">
-        <v>-0.561406</v>
+        <v>0.7354619999999999</v>
       </c>
       <c r="O410" s="5" t="n">
-        <v>-0.228335</v>
+        <v>-0.018459</v>
       </c>
       <c r="P410" t="inlineStr">
         <is>
@@ -51618,10 +51384,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R410" s="5" t="n">
+        <v>1.471725</v>
       </c>
       <c r="S410" t="inlineStr">
         <is>
@@ -51652,12 +51416,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Other (expense) income</t>
+          <t>Operating (loss) income</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -51681,16 +51445,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I411" s="5" t="n">
+        <v>864.888</v>
       </c>
       <c r="J411" s="5" t="n">
-        <v>0.018388</v>
-      </c>
-      <c r="K411" s="5" t="n">
-        <v>-0.080022</v>
+        <v>-6136.368</v>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -51702,11 +51466,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N411" s="5" t="n">
-        <v>0.068939</v>
-      </c>
-      <c r="O411" s="5" t="n">
-        <v>-0.005299</v>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P411" t="inlineStr">
         <is>
@@ -51718,15 +51486,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R411" s="5" t="n">
+        <v>0.211795</v>
+      </c>
+      <c r="S411" s="5" t="n">
+        <v>-2.611497</v>
       </c>
       <c r="T411" t="inlineStr">
         <is>
@@ -51757,10 +51521,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Gain (loss) on disposal of assets</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -51781,58 +51549,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I412" s="5" t="n">
+        <v>-381.623</v>
+      </c>
+      <c r="J412" s="5" t="n">
+        <v>-0.108842</v>
+      </c>
+      <c r="K412" s="5" t="n">
+        <v>-0.378725</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M412" s="5" t="n">
+        <v>-0.498511</v>
       </c>
       <c r="N412" s="5" t="n">
-        <v>0.317692</v>
-      </c>
-      <c r="O412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.561406</v>
+      </c>
+      <c r="O412" s="5" t="n">
+        <v>-0.228335</v>
+      </c>
+      <c r="P412" s="5" t="n">
+        <v>-0.202701</v>
+      </c>
+      <c r="Q412" s="5" t="n">
+        <v>-0.241864</v>
+      </c>
+      <c r="R412" s="5" t="n">
+        <v>-0.087695</v>
+      </c>
+      <c r="S412" s="5" t="n">
+        <v>-0.007868999999999999</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -51863,14 +51613,10 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Current income tax expense (Note 14)</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Write-down of exploration and evaluation assets (Note 9)</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -51901,22 +51647,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K413" s="5" t="n">
-        <v>74.002</v>
-      </c>
-      <c r="L413" s="5" t="n">
-        <v>122.257</v>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N413" s="5" t="n">
-        <v>0.015521</v>
-      </c>
-      <c r="O413" s="5" t="n">
-        <v>0.000281</v>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -51928,15 +51682,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R413" s="5" t="n">
+        <v>-0.033451</v>
+      </c>
+      <c r="S413" s="5" t="n">
+        <v>-0.222182</v>
       </c>
       <c r="T413" t="inlineStr">
         <is>
@@ -51967,10 +51717,14 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Deferred income tax (recovery) expense (Note 14)</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>(Loss) income before taxes</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -52016,11 +51770,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N414" s="5" t="n">
-        <v>0.52501</v>
-      </c>
-      <c r="O414" s="5" t="n">
-        <v>-0.010251</v>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -52032,15 +51790,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R414" s="5" t="n">
+        <v>0.276116</v>
+      </c>
+      <c r="S414" s="5" t="n">
+        <v>-2.589458</v>
       </c>
       <c r="T414" t="inlineStr">
         <is>
@@ -52071,12 +51825,12 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Loss per share – Basic and Diluted (Note 13(d)) $</t>
+          <t>Current income tax expense (Note 14)</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -52109,15 +51863,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K415" s="5" t="n">
+        <v>74.002</v>
+      </c>
+      <c r="L415" s="5" t="n">
+        <v>122.257</v>
       </c>
       <c r="M415" t="inlineStr">
         <is>
@@ -52125,30 +51875,24 @@
         </is>
       </c>
       <c r="N415" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.015521</v>
       </c>
       <c r="O415" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.000281</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q415" s="5" t="n">
+        <v>0.20074</v>
+      </c>
+      <c r="R415" s="5" t="n">
+        <v>0.173209</v>
+      </c>
+      <c r="S415" s="5" t="n">
+        <v>0.0284</v>
       </c>
       <c r="T415" t="inlineStr">
         <is>
@@ -52179,10 +51923,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – Basic and Diluted</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
+          <t>Deferred income tax expense (Note 14)</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -52218,17 +51966,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L416" s="5" t="n">
-        <v>68128.24400000001</v>
-      </c>
-      <c r="M416" s="5" t="n">
-        <v>79442.77099999999</v>
-      </c>
-      <c r="N416" s="5" t="n">
-        <v>85.56684</v>
-      </c>
-      <c r="O416" s="5" t="n">
-        <v>85.744944</v>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -52240,15 +51996,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R416" s="5" t="n">
+        <v>0.648242</v>
+      </c>
+      <c r="S416" s="5" t="n">
+        <v>0.544929</v>
       </c>
       <c r="T416" t="inlineStr">
         <is>
@@ -52274,17 +52026,17 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Operating expenses (Note 10)</t>
+          <t>Loss per share – basic and diluted (Note 13(d)) $</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -52317,14 +52069,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K417" s="5" t="n">
-        <v>12034.223</v>
-      </c>
-      <c r="L417" s="5" t="n">
-        <v>12630.791</v>
-      </c>
-      <c r="M417" s="5" t="n">
-        <v>12984.236</v>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N417" t="inlineStr">
         <is>
@@ -52346,15 +52104,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R417" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S417" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -52385,10 +52139,14 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Mine operating earnings (loss)</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr"/>
+          <t>Mine operating income</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -52424,11 +52182,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L418" s="5" t="n">
-        <v>-101.006</v>
-      </c>
-      <c r="M418" s="5" t="n">
-        <v>1368.6</v>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N418" t="inlineStr">
         <is>
@@ -52445,15 +52207,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q418" s="5" t="n">
+        <v>3.249304</v>
+      </c>
+      <c r="R418" s="5" t="n">
+        <v>3.425841</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
@@ -52489,10 +52247,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 12(b))</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr"/>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -52508,15 +52270,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H419" s="5" t="n">
+        <v>10471.621</v>
+      </c>
+      <c r="I419" s="5" t="n">
+        <v>864.888</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>
@@ -52533,8 +52291,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M419" s="5" t="n">
-        <v>747.444</v>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N419" t="inlineStr">
         <is>
@@ -52551,15 +52311,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q419" s="5" t="n">
+        <v>1.258543</v>
+      </c>
+      <c r="R419" s="5" t="n">
+        <v>0.211795</v>
       </c>
       <c r="S419" t="inlineStr">
         <is>
@@ -52595,14 +52351,10 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Foreign exchange (loss) gain</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Loss on disposal of assets</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -52613,14 +52365,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G420" s="5" t="n">
-        <v>-0.167509</v>
-      </c>
-      <c r="H420" s="5" t="n">
-        <v>1042.168</v>
-      </c>
-      <c r="I420" s="5" t="n">
-        <v>-381.623</v>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
@@ -52632,11 +52390,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L420" s="5" t="n">
-        <v>62.856</v>
-      </c>
-      <c r="M420" s="5" t="n">
-        <v>-498.511</v>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N420" t="inlineStr">
         <is>
@@ -52648,15 +52410,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P420" s="5" t="n">
+        <v>-0.004518</v>
+      </c>
+      <c r="Q420" s="5" t="n">
+        <v>-0.001857</v>
       </c>
       <c r="R420" t="inlineStr">
         <is>
@@ -52697,10 +52455,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>(Loss) gain on disposal of assets</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr"/>
+          <t>Income before taxes</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -52736,11 +52498,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L421" s="5" t="n">
-        <v>11.645</v>
-      </c>
-      <c r="M421" s="5" t="n">
-        <v>-15.448</v>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N421" t="inlineStr">
         <is>
@@ -52757,15 +52523,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q421" s="5" t="n">
+        <v>1.100318</v>
+      </c>
+      <c r="R421" s="5" t="n">
+        <v>0.276116</v>
       </c>
       <c r="S421" t="inlineStr">
         <is>
@@ -52801,10 +52563,14 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets (Note 7)</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>Deferred income tax (recovery) (Note 14)</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -52840,11 +52606,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L422" s="5" t="n">
-        <v>-555.889</v>
-      </c>
-      <c r="M422" s="5" t="n">
-        <v>-40.822</v>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N422" t="inlineStr">
         <is>
@@ -52861,15 +52631,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q422" s="5" t="n">
+        <v>-1.401434</v>
+      </c>
+      <c r="R422" s="5" t="n">
+        <v>0.648242</v>
       </c>
       <c r="S422" t="inlineStr">
         <is>
@@ -52905,12 +52671,12 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Current income tax expense (Note 13)</t>
+          <t>Net income (loss) $</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -52948,11 +52714,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L423" s="5" t="n">
-        <v>122.257</v>
-      </c>
-      <c r="M423" s="5" t="n">
-        <v>134.485</v>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N423" t="inlineStr">
         <is>
@@ -52969,15 +52739,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q423" s="5" t="n">
+        <v>2.301012</v>
+      </c>
+      <c r="R423" s="5" t="n">
+        <v>-0.545335</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
@@ -53008,17 +52774,17 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Earnings (loss) per share)</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery) (Note 13)</t>
+          <t>Basic $</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -53056,11 +52822,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L424" s="5" t="n">
-        <v>-353.664</v>
-      </c>
-      <c r="M424" s="5" t="n">
-        <v>160.598</v>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N424" t="inlineStr">
         <is>
@@ -53077,15 +52847,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q424" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="R424" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -53116,17 +52882,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Earnings (loss) per share)</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Loss per share – Basic and Diluted (Note 12(d)) $</t>
+          <t>Diluted $</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -53164,11 +52930,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L425" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="M425" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N425" t="inlineStr">
         <is>
@@ -53185,15 +52955,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q425" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="R425" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>
@@ -53224,15 +52990,19 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2014 68,128,244 53,495,947 - 4,776,173 (168,798)</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -53268,11 +53038,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L426" s="5" t="n">
-        <v>49744.653</v>
-      </c>
-      <c r="M426" s="5" t="n">
-        <v>-8358.669</v>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N426" t="inlineStr">
         <is>
@@ -53289,15 +53063,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q426" s="5" t="n">
+        <v>121.930731</v>
+      </c>
+      <c r="R426" s="5" t="n">
+        <v>144.617071</v>
       </c>
       <c r="S426" t="inlineStr">
         <is>
@@ -53328,17 +53098,17 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
+          <t>Diluted</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>DilutedAverageShares</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -53376,11 +53146,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L427" s="5" t="n">
-        <v>-1427.838</v>
-      </c>
-      <c r="M427" s="5" t="n">
-        <v>-1427.838</v>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N427" t="inlineStr">
         <is>
@@ -53397,15 +53171,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q427" s="5" t="n">
+        <v>131.913313</v>
+      </c>
+      <c r="R427" s="5" t="n">
+        <v>144.617071</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
@@ -53434,17 +53204,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Cumulative translation</t>
-        </is>
-      </c>
+      <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustments - - - - 941,222</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr"/>
+          <t>Revenues (Note 8) $</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -53475,11 +53245,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K428" s="5" t="n">
-        <v>941.222</v>
-      </c>
-      <c r="L428" s="5" t="n">
-        <v>941.222</v>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M428" t="inlineStr">
         <is>
@@ -53491,15 +53265,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O428" s="5" t="n">
+        <v>13.098339</v>
+      </c>
+      <c r="P428" s="5" t="n">
+        <v>13.311376</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -53540,12 +53310,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Cumulative translation</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Unrealized loss on investments - - - - (12,500)</t>
+          <t>Share-based payments (Note 15(b))</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -53579,11 +53349,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K429" s="5" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="L429" s="5" t="n">
-        <v>-12.5</v>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M429" t="inlineStr">
         <is>
@@ -53595,15 +53369,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O429" s="5" t="n">
+        <v>-0.018459</v>
+      </c>
+      <c r="P429" s="5" t="n">
+        <v>0.414061</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -53644,15 +53414,19 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Cumulative translation</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2015 68,128,244 53,495,947 - 4,776,173 759,924</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr"/>
+          <t>Other expense</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -53683,29 +53457,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K430" s="5" t="n">
-        <v>49245.537</v>
-      </c>
-      <c r="L430" s="5" t="n">
-        <v>49245.537</v>
-      </c>
-      <c r="M430" s="5" t="n">
-        <v>-9786.507</v>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N430" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O430" s="5" t="n">
+        <v>-0.005299</v>
+      </c>
+      <c r="P430" s="5" t="n">
+        <v>-0.018648</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -53746,19 +53522,15 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Cumulative translation</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-down of property, plant and equipment (Note 9)</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -53794,11 +53566,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L431" s="5" t="n">
-        <v>-1939.278</v>
-      </c>
-      <c r="M431" s="5" t="n">
-        <v>-1939.278</v>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N431" t="inlineStr">
         <is>
@@ -53810,10 +53586,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P431" s="5" t="n">
+        <v>-0.526639</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -53854,15 +53628,19 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Shares issued in relation to</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Shares issued in relation to private placements 17,438,596 7,620,000 - - -</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr"/>
+          <t>Current income tax expense (Note 16)</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -53898,8 +53676,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L432" s="5" t="n">
-        <v>7620</v>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
@@ -53911,15 +53691,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O432" s="5" t="n">
+        <v>0.000281</v>
+      </c>
+      <c r="P432" s="5" t="n">
+        <v>0.017649</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -53960,15 +53736,19 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Shares issued in relation to</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Share issue costs - (491,147) - - -</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr"/>
+          <t>Deferred income tax (recovery) (Note 16)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -54004,8 +53784,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L433" s="5" t="n">
-        <v>-491.147</v>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M433" t="inlineStr">
         <is>
@@ -54017,15 +53799,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O433" s="5" t="n">
+        <v>-0.010251</v>
+      </c>
+      <c r="P433" s="5" t="n">
+        <v>-0.420018</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -54066,15 +53844,19 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Warrants issued in relation to</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Warrants issued in relation to private placements - (973,378) 973,378 - -</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr"/>
+          <t>Loss per share – Basic and Diluted (Note 15(d)) $</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -54125,15 +53907,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O434" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="P434" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -54174,12 +53952,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Shared based compensation</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Shared based compensation expense - - - 747,444 -</t>
+          <t>Weighted average number of shares outstanding – Basic and Diluted</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -54219,27 +53997,19 @@
         </is>
       </c>
       <c r="L435" s="5" t="n">
-        <v>747.444</v>
-      </c>
-      <c r="M435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>68128.24400000001</v>
+      </c>
+      <c r="M435" s="5" t="n">
+        <v>79.44277099999999</v>
+      </c>
+      <c r="N435" s="5" t="n">
+        <v>85.56684</v>
+      </c>
+      <c r="O435" s="5" t="n">
+        <v>85.744944</v>
+      </c>
+      <c r="P435" s="5" t="n">
+        <v>99.794121</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -54280,15 +54050,19 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Cumulative translation</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustments - - - - (7,548,807)</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr"/>
+          <t>Operating expenses (Note 11)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -54304,15 +54078,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H436" s="5" t="n">
+        <v>10125.634</v>
+      </c>
+      <c r="I436" s="5" t="n">
+        <v>10314.273</v>
       </c>
       <c r="J436" t="inlineStr">
         <is>
@@ -54324,23 +54094,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L436" s="5" t="n">
-        <v>-7548.807</v>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M436" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N436" s="5" t="n">
+        <v>14.894005</v>
+      </c>
+      <c r="O436" s="5" t="n">
+        <v>14.777527</v>
       </c>
       <c r="P436" t="inlineStr">
         <is>
@@ -54386,12 +54154,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Cumulative translation</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Unrealized loss on investments - - - - (1,250)</t>
+          <t>Other (expense) income</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -54420,33 +54188,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L437" s="5" t="n">
-        <v>-1.25</v>
+      <c r="J437" s="5" t="n">
+        <v>0.018388</v>
+      </c>
+      <c r="K437" s="5" t="n">
+        <v>-0.080022</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M437" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N437" s="5" t="n">
+        <v>0.068939</v>
+      </c>
+      <c r="O437" s="5" t="n">
+        <v>-0.005299</v>
       </c>
       <c r="P437" t="inlineStr">
         <is>
@@ -54492,12 +54254,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Cumulative translation</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2016 85,566,840 59,651,422 973,378 5,523,617 (6,790,133)</t>
+          <t>Gain (loss) on disposal of assets</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -54536,16 +54298,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L438" s="5" t="n">
-        <v>47632.499</v>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M438" s="5" t="n">
-        <v>-11725.785</v>
-      </c>
-      <c r="N438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.015448</v>
+      </c>
+      <c r="N438" s="5" t="n">
+        <v>0.317692</v>
       </c>
       <c r="O438" t="inlineStr">
         <is>
@@ -54596,15 +54358,19 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr"/>
+          <t>Deferred income tax (recovery) expense (Note 14)</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -54615,20 +54381,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G439" s="5" t="n">
-        <v>0.411462</v>
-      </c>
-      <c r="H439" s="5" t="n">
-        <v>694.141</v>
-      </c>
-      <c r="I439" s="5" t="n">
-        <v>951.408</v>
-      </c>
-      <c r="J439" s="5" t="n">
-        <v>1.474293</v>
-      </c>
-      <c r="K439" s="5" t="n">
-        <v>145.681</v>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
@@ -54640,15 +54416,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N439" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O439" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N439" s="5" t="n">
+        <v>0.52501</v>
+      </c>
+      <c r="O439" s="5" t="n">
+        <v>-0.010251</v>
       </c>
       <c r="P439" t="inlineStr">
         <is>
@@ -54699,12 +54471,12 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Loss per share – Basic and Diluted (Note 13(d)) $</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -54737,26 +54509,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K440" s="5" t="n">
-        <v>-80.02200000000001</v>
-      </c>
-      <c r="L440" s="5" t="n">
-        <v>410.704</v>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N440" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="O440" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="P440" t="inlineStr">
         <is>
@@ -54802,15 +54574,19 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Gain on sale of available-for-sale investments (Note 7(b))</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr"/>
+          <t>Operating expenses (Note 10)</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -54842,22 +54618,16 @@
         </is>
       </c>
       <c r="K441" s="5" t="n">
-        <v>237.471</v>
-      </c>
-      <c r="L441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12034.223</v>
+      </c>
+      <c r="L441" s="5" t="n">
+        <v>12630.791</v>
+      </c>
+      <c r="M441" s="5" t="n">
+        <v>12.984236</v>
+      </c>
+      <c r="N441" s="5" t="n">
+        <v>14.894005</v>
       </c>
       <c r="O441" t="inlineStr">
         <is>
@@ -54908,12 +54678,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets (Note 7(a))</t>
+          <t>Mine operating (loss) earnings</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -54942,28 +54712,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L442" s="5" t="n">
-        <v>-555.889</v>
-      </c>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J442" s="5" t="n">
+        <v>0.155916</v>
+      </c>
+      <c r="K442" s="5" t="n">
+        <v>-2.572319</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M442" s="5" t="n">
+        <v>1.3686</v>
+      </c>
+      <c r="N442" s="5" t="n">
+        <v>-1.741018</v>
       </c>
       <c r="O442" t="inlineStr">
         <is>
@@ -55014,12 +54778,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (Note 14)</t>
+          <t>Share-based payments (Note 12(b))</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -55053,21 +54817,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K443" s="5" t="n">
-        <v>-1217.391</v>
-      </c>
-      <c r="L443" s="5" t="n">
-        <v>-353.664</v>
-      </c>
-      <c r="M443" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N443" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M443" s="5" t="n">
+        <v>0.747444</v>
+      </c>
+      <c r="N443" s="5" t="n">
+        <v>0.7354619999999999</v>
       </c>
       <c r="O443" t="inlineStr">
         <is>
@@ -55123,14 +54887,10 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Loss per share – Basic (Note 13(c)) $</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Write-down of exploration and evaluation assets (Note 7)</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -55161,16 +54921,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K444" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L444" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="M444" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-555.889</v>
+      </c>
+      <c r="M444" s="5" t="n">
+        <v>-0.040822</v>
       </c>
       <c r="N444" t="inlineStr">
         <is>
@@ -55231,10 +54991,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>– Diluted (Note 13(c)) $</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr"/>
+          <t>Current income tax expense (Note 13)</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -55265,21 +55029,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K445" s="5" t="n">
-        <v>-5e-05</v>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L445" s="5" t="n">
-        <v>-2e-05</v>
-      </c>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>122.257</v>
+      </c>
+      <c r="M445" s="5" t="n">
+        <v>0.134485</v>
+      </c>
+      <c r="N445" s="5" t="n">
+        <v>0.015521</v>
       </c>
       <c r="O445" t="inlineStr">
         <is>
@@ -55335,12 +55097,12 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – Basic</t>
+          <t>Deferred income tax expense (Note 13)</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -55353,33 +55115,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G446" s="5" t="n">
-        <v>49.438882</v>
-      </c>
-      <c r="H446" s="5" t="n">
-        <v>65.159606</v>
-      </c>
-      <c r="I446" s="5" t="n">
-        <v>68.061035</v>
-      </c>
-      <c r="J446" s="5" t="n">
-        <v>68.128244</v>
-      </c>
-      <c r="K446" s="5" t="n">
-        <v>68.128244</v>
-      </c>
-      <c r="L446" s="5" t="n">
-        <v>68.128244</v>
-      </c>
-      <c r="M446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M446" s="5" t="n">
+        <v>0.160598</v>
+      </c>
+      <c r="N446" s="5" t="n">
+        <v>0.52501</v>
       </c>
       <c r="O446" t="inlineStr">
         <is>
@@ -55435,10 +55205,14 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – Diluted</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr"/>
+          <t>Loss per share – Basic and Diluted (Note 12(d)) $</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -55449,33 +55223,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G447" s="5" t="n">
-        <v>50.434322</v>
-      </c>
-      <c r="H447" s="5" t="n">
-        <v>66.76100599999999</v>
-      </c>
-      <c r="I447" s="5" t="n">
-        <v>68061.035</v>
-      </c>
-      <c r="J447" s="5" t="n">
-        <v>68.128244</v>
-      </c>
-      <c r="K447" s="5" t="n">
-        <v>68128.24400000001</v>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L447" s="5" t="n">
-        <v>68128.24400000001</v>
-      </c>
-      <c r="M447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="M447" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="N447" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="O447" t="inlineStr">
         <is>
@@ -55526,12 +55306,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Balance at January 1, 2014 68,128,244 53,495,947 - 4,630,492 867,142</t>
+          <t>Mine operating earnings (loss)</t>
         </is>
       </c>
       <c r="D448" t="inlineStr"/>
@@ -55565,16 +55345,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K448" s="5" t="n">
-        <v>54121.666</v>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L448" s="5" t="n">
-        <v>-4871.915</v>
-      </c>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-101.006</v>
+      </c>
+      <c r="M448" s="5" t="n">
+        <v>1368.6</v>
       </c>
       <c r="N448" t="inlineStr">
         <is>
@@ -55630,17 +55410,17 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Loss for the year - - - - -</t>
+          <t>Foreign exchange (loss) gain</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -55653,36 +55433,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G449" s="5" t="n">
+        <v>-0.167509</v>
+      </c>
+      <c r="H449" s="5" t="n">
+        <v>1042.168</v>
+      </c>
+      <c r="I449" s="5" t="n">
+        <v>-381.623</v>
       </c>
       <c r="J449" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K449" s="5" t="n">
-        <v>-3486.754</v>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L449" s="5" t="n">
-        <v>-3486.754</v>
-      </c>
-      <c r="M449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>62.856</v>
+      </c>
+      <c r="M449" s="5" t="n">
+        <v>-498.511</v>
       </c>
       <c r="N449" t="inlineStr">
         <is>
@@ -55738,12 +55512,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Share based payments expense - - - 145,681 -</t>
+          <t>(Loss) gain on disposal of assets</t>
         </is>
       </c>
       <c r="D450" t="inlineStr"/>
@@ -55777,18 +55551,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K450" s="5" t="n">
-        <v>145.681</v>
-      </c>
-      <c r="L450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L450" s="5" t="n">
+        <v>11.645</v>
+      </c>
+      <c r="M450" s="5" t="n">
+        <v>-15.448</v>
       </c>
       <c r="N450" t="inlineStr">
         <is>
@@ -55844,15 +55616,19 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Cumulative translation</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustments - - - - (1,035,940)</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr"/>
+          <t>Deferred income tax expense (recovery) (Note 13)</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -55883,18 +55659,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K451" s="5" t="n">
-        <v>-1035.94</v>
-      </c>
-      <c r="L451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L451" s="5" t="n">
+        <v>-353.664</v>
+      </c>
+      <c r="M451" s="5" t="n">
+        <v>160.598</v>
       </c>
       <c r="N451" t="inlineStr">
         <is>
@@ -55950,7 +55724,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Cumulative translation</t>
+          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -55989,16 +55763,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K452" s="5" t="n">
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L452" s="5" t="n">
         <v>49744.653</v>
       </c>
-      <c r="L452" s="5" t="n">
+      <c r="M452" s="5" t="n">
         <v>-8358.669</v>
-      </c>
-      <c r="M452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="N452" t="inlineStr">
         <is>
@@ -56054,12 +55828,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Cumulative translation</t>
+          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Loss for the year - - - - -</t>
+          <t>Net loss for the year - - - - -</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -56097,16 +55871,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K453" s="5" t="n">
-        <v>-1427.838</v>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L453" s="5" t="n">
         <v>-1427.838</v>
       </c>
-      <c r="M453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M453" s="5" t="n">
+        <v>-1427.838</v>
       </c>
       <c r="N453" t="inlineStr">
         <is>
@@ -56162,19 +55936,15 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Operating expenses (Note 12)</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Cumulative translation adjustments - - - - 941,222</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -56195,19 +55965,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I454" s="5" t="n">
-        <v>10314.273</v>
-      </c>
-      <c r="J454" s="5" t="n">
-        <v>11.717504</v>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K454" s="5" t="n">
-        <v>12.034223</v>
-      </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>941.222</v>
+      </c>
+      <c r="L454" s="5" t="n">
+        <v>941.222</v>
       </c>
       <c r="M454" t="inlineStr">
         <is>
@@ -56268,12 +56040,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Mine operating (loss) earnings</t>
+          <t>Unrealized loss on investments - - - - (12,500)</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
@@ -56302,16 +56074,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J455" s="5" t="n">
-        <v>0.155916</v>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K455" s="5" t="n">
-        <v>-2.572319</v>
-      </c>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-12.5</v>
+      </c>
+      <c r="L455" s="5" t="n">
+        <v>-12.5</v>
       </c>
       <c r="M455" t="inlineStr">
         <is>
@@ -56372,12 +56144,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Property investigations</t>
+          <t>Balance at December 31, 2015 68,128,244 53,495,947 - 4,776,173 759,924</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
@@ -56406,23 +56178,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J456" s="5" t="n">
-        <v>0.178508</v>
-      </c>
-      <c r="K456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K456" s="5" t="n">
+        <v>49245.537</v>
+      </c>
+      <c r="L456" s="5" t="n">
+        <v>49245.537</v>
+      </c>
+      <c r="M456" s="5" t="n">
+        <v>-9786.507</v>
       </c>
       <c r="N456" t="inlineStr">
         <is>
@@ -56478,15 +56246,19 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties (Note 8(a))</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr"/>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -56512,23 +56284,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J457" s="5" t="n">
-        <v>2.583765</v>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L457" s="5" t="n">
+        <v>-1939.278</v>
+      </c>
+      <c r="M457" s="5" t="n">
+        <v>-1939.278</v>
       </c>
       <c r="N457" t="inlineStr">
         <is>
@@ -56584,12 +56354,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Shares issued in relation to</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of available-for-sale investments (Note 8(b))</t>
+          <t>Shares issued in relation to private placements 17,438,596 7,620,000 - - -</t>
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
@@ -56618,16 +56388,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J458" s="5" t="n">
-        <v>-0.803305</v>
-      </c>
-      <c r="K458" s="5" t="n">
-        <v>0.237471</v>
-      </c>
-      <c r="L458" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L458" s="5" t="n">
+        <v>7620</v>
       </c>
       <c r="M458" t="inlineStr">
         <is>
@@ -56688,19 +56460,15 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Shares issued in relation to</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Current income tax expense</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Share issue costs - (491,147) - - -</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -56711,27 +56479,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G459" s="5" t="n">
-        <v>-1.555409</v>
-      </c>
-      <c r="H459" s="5" t="n">
-        <v>-3531.865</v>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J459" s="5" t="n">
-        <v>0.050663</v>
-      </c>
-      <c r="K459" s="5" t="n">
-        <v>0.074002</v>
-      </c>
-      <c r="L459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L459" s="5" t="n">
+        <v>-491.147</v>
       </c>
       <c r="M459" t="inlineStr">
         <is>
@@ -56792,12 +56566,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Warrants issued in relation to</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Deferred income tax (recovery) expense</t>
+          <t>Warrants issued in relation to private placements - (973,378) 973,378 - -</t>
         </is>
       </c>
       <c r="D460" t="inlineStr"/>
@@ -56826,11 +56600,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J460" s="5" t="n">
-        <v>1.577243</v>
-      </c>
-      <c r="K460" s="5" t="n">
-        <v>-1.217391</v>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
@@ -56896,19 +56674,15 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Shared based compensation</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Loss per share – Basic (Note 16(c)) $</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Shared based compensation expense - - - 747,444 -</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -56934,16 +56708,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J461" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="K461" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="L461" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L461" s="5" t="n">
+        <v>747.444</v>
       </c>
       <c r="M461" t="inlineStr">
         <is>
@@ -57004,12 +56780,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>– Diluted (Note 16(c)) $</t>
+          <t>Cumulative translation adjustments - - - - (7,548,807)</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
@@ -57038,16 +56814,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J462" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="K462" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L462" s="5" t="n">
+        <v>-7548.807</v>
       </c>
       <c r="M462" t="inlineStr">
         <is>
@@ -57108,19 +56886,15 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Mine operating earnings</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Unrealized loss on investments - - - - (1,250)</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -57131,27 +56905,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G463" s="5" t="n">
-        <v>7.435484</v>
-      </c>
-      <c r="H463" s="5" t="n">
-        <v>12897.344</v>
-      </c>
-      <c r="I463" s="5" t="n">
-        <v>4035.981</v>
-      </c>
-      <c r="J463" s="5" t="n">
-        <v>515.812</v>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K463" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L463" s="5" t="n">
+        <v>-1.25</v>
       </c>
       <c r="M463" t="inlineStr">
         <is>
@@ -57212,12 +56992,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Ofﬁce, rent, insurance and sundry</t>
+          <t>Balance at December 31, 2016 85,566,840 59,651,422 973,378 5,523,617 (6,790,133)</t>
         </is>
       </c>
       <c r="D464" t="inlineStr"/>
@@ -57241,26 +57021,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I464" s="5" t="n">
-        <v>513.9299999999999</v>
-      </c>
-      <c r="J464" s="5" t="n">
-        <v>340.789</v>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K464" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L464" s="5" t="n">
+        <v>47632.499</v>
+      </c>
+      <c r="M464" s="5" t="n">
+        <v>-11725.785</v>
       </c>
       <c r="N464" t="inlineStr">
         <is>
@@ -57321,7 +57101,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Ofﬁce salaries and services</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D465" t="inlineStr"/>
@@ -57335,26 +57115,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G465" s="5" t="n">
+        <v>0.411462</v>
+      </c>
+      <c r="H465" s="5" t="n">
+        <v>694.141</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>890.379</v>
+        <v>951.408</v>
       </c>
       <c r="J465" s="5" t="n">
-        <v>880.22</v>
-      </c>
-      <c r="K465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.474293</v>
+      </c>
+      <c r="K465" s="5" t="n">
+        <v>145.681</v>
       </c>
       <c r="L465" t="inlineStr">
         <is>
@@ -57420,15 +57194,19 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Write-down of inventory (Note 6)</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr"/>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -57454,18 +57232,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J466" s="5" t="n">
-        <v>359.896</v>
-      </c>
-      <c r="K466" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L466" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K466" s="5" t="n">
+        <v>-80.02200000000001</v>
+      </c>
+      <c r="L466" s="5" t="n">
+        <v>410.704</v>
       </c>
       <c r="M466" t="inlineStr">
         <is>
@@ -57526,12 +57302,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties (Note 8 (a))</t>
+          <t>Gain on sale of available-for-sale investments (Note 7(b))</t>
         </is>
       </c>
       <c r="D467" t="inlineStr"/>
@@ -57560,13 +57336,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J467" s="5" t="n">
-        <v>2583.765</v>
-      </c>
-      <c r="K467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K467" s="5" t="n">
+        <v>237.471</v>
       </c>
       <c r="L467" t="inlineStr">
         <is>
@@ -57632,12 +57408,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Operating (loss) income</t>
+          <t>Write-down of exploration and evaluation assets (Note 7(a))</t>
         </is>
       </c>
       <c r="D468" t="inlineStr"/>
@@ -57661,21 +57437,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I468" s="5" t="n">
-        <v>864.888</v>
-      </c>
-      <c r="J468" s="5" t="n">
-        <v>-6136.368</v>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L468" s="5" t="n">
+        <v>-555.889</v>
       </c>
       <c r="M468" t="inlineStr">
         <is>
@@ -57741,10 +57519,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Write-down of available-for-sale investment (Note 8 (b))</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr"/>
+          <t>Deferred income tax recovery (Note 14)</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -57765,21 +57547,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I469" s="5" t="n">
-        <v>-750</v>
-      </c>
-      <c r="J469" s="5" t="n">
-        <v>-803.3049999999999</v>
-      </c>
-      <c r="K469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K469" s="5" t="n">
+        <v>-1217.391</v>
+      </c>
+      <c r="L469" s="5" t="n">
+        <v>-353.664</v>
       </c>
       <c r="M469" t="inlineStr">
         <is>
@@ -57845,12 +57627,12 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Deferred income tax expense</t>
+          <t>Loss per share – Basic (Note 13(c)) $</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -57863,27 +57645,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G470" s="5" t="n">
-        <v>-0.481201</v>
-      </c>
-      <c r="H470" s="5" t="n">
-        <v>-617.335</v>
-      </c>
-      <c r="I470" s="5" t="n">
-        <v>1104.009</v>
-      </c>
-      <c r="J470" s="5" t="n">
-        <v>1577.243</v>
-      </c>
-      <c r="K470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K470" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="L470" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="M470" t="inlineStr">
         <is>
@@ -57949,14 +57735,10 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Loss per share – Basic (Note 16 (c)) $</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>– Diluted (Note 13(c)) $</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -57977,21 +57759,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I471" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J471" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="K471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K471" s="5" t="n">
+        <v>-5e-05</v>
+      </c>
+      <c r="L471" s="5" t="n">
+        <v>-2e-05</v>
       </c>
       <c r="M471" t="inlineStr">
         <is>
@@ -58057,10 +57839,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>– Diluted (Note 16 (c)) $</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding – Basic</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -58071,31 +57857,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G472" s="5" t="n">
+        <v>49.438882</v>
+      </c>
+      <c r="H472" s="5" t="n">
+        <v>65.159606</v>
       </c>
       <c r="I472" s="5" t="n">
-        <v>-2e-05</v>
+        <v>68.061035</v>
       </c>
       <c r="J472" s="5" t="n">
-        <v>-0.00013</v>
-      </c>
-      <c r="K472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>68.128244</v>
+      </c>
+      <c r="K472" s="5" t="n">
+        <v>68.128244</v>
+      </c>
+      <c r="L472" s="5" t="n">
+        <v>68.128244</v>
       </c>
       <c r="M472" t="inlineStr">
         <is>
@@ -58156,12 +57934,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Accounting audit and legal</t>
+          <t>Weighted average number of shares outstanding – Diluted</t>
         </is>
       </c>
       <c r="D473" t="inlineStr"/>
@@ -58175,31 +57953,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G473" s="5" t="n">
+        <v>50.434322</v>
       </c>
       <c r="H473" s="5" t="n">
-        <v>225.566</v>
+        <v>66.76100599999999</v>
       </c>
       <c r="I473" s="5" t="n">
-        <v>228.47</v>
-      </c>
-      <c r="J473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>68061.035</v>
+      </c>
+      <c r="J473" s="5" t="n">
+        <v>68.128244</v>
+      </c>
+      <c r="K473" s="5" t="n">
+        <v>68128.24400000001</v>
+      </c>
+      <c r="L473" s="5" t="n">
+        <v>68128.24400000001</v>
       </c>
       <c r="M473" t="inlineStr">
         <is>
@@ -58260,19 +58030,15 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Operating income</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Balance at January 1, 2014 68,128,244 53,495,947 - 4,630,492 867,142</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -58288,26 +58054,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H474" s="5" t="n">
-        <v>10471.621</v>
-      </c>
-      <c r="I474" s="5" t="n">
-        <v>864.888</v>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L474" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K474" s="5" t="n">
+        <v>54121.666</v>
+      </c>
+      <c r="L474" s="5" t="n">
+        <v>-4871.915</v>
       </c>
       <c r="M474" t="inlineStr">
         <is>
@@ -58368,17 +58134,17 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Loss for the year - - - - -</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -58391,29 +58157,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G475" s="5" t="n">
-        <v>0.01079</v>
-      </c>
-      <c r="H475" s="5" t="n">
-        <v>211.575</v>
-      </c>
-      <c r="I475" s="5" t="n">
-        <v>223.159</v>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K475" s="5" t="n">
+        <v>-3486.754</v>
+      </c>
+      <c r="L475" s="5" t="n">
+        <v>-3486.754</v>
       </c>
       <c r="M475" t="inlineStr">
         <is>
@@ -58474,12 +58242,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Outstanding              ($)            ($)               ($)                    ($)                  ($)                 ($)</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Write-down of available for sale investment (Note 20)</t>
+          <t>Share based payments expense - - - 145,681 -</t>
         </is>
       </c>
       <c r="D476" t="inlineStr"/>
@@ -58503,18 +58271,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I476" s="5" t="n">
-        <v>-750</v>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K476" s="5" t="n">
+        <v>145.681</v>
       </c>
       <c r="L476" t="inlineStr">
         <is>
@@ -58580,12 +58348,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Earnings (loss) before taxes</t>
+          <t>Cumulative translation adjustments - - - - (1,035,940)</t>
         </is>
       </c>
       <c r="D477" t="inlineStr"/>
@@ -58604,21 +58372,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H477" s="5" t="n">
-        <v>11725.49</v>
-      </c>
-      <c r="I477" s="5" t="n">
-        <v>-40.837</v>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K477" s="5" t="n">
+        <v>-1035.94</v>
       </c>
       <c r="L477" t="inlineStr">
         <is>
@@ -58684,19 +58454,15 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Net earnings</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at December 31, 2014 68,128,244 53,495,947 - 4,776,173 (168,798)</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -58707,29 +58473,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G478" s="5" t="n">
-        <v>3.434169</v>
-      </c>
-      <c r="H478" s="5" t="n">
-        <v>7576.29</v>
-      </c>
-      <c r="I478" s="5" t="n">
-        <v>-1144.846</v>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K478" s="5" t="n">
+        <v>49744.653</v>
+      </c>
+      <c r="L478" s="5" t="n">
+        <v>-8358.669</v>
       </c>
       <c r="M478" t="inlineStr">
         <is>
@@ -58790,15 +58558,19 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Cumulative translation</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Retained Earnings (Deficit) - Beginning of year</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr"/>
+          <t>Loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -58814,26 +58586,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H479" s="5" t="n">
-        <v>-2784.351</v>
-      </c>
-      <c r="I479" s="5" t="n">
-        <v>4791.939</v>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L479" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K479" s="5" t="n">
+        <v>-1427.838</v>
+      </c>
+      <c r="L479" s="5" t="n">
+        <v>-1427.838</v>
       </c>
       <c r="M479" t="inlineStr">
         <is>
@@ -58894,12 +58666,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Retained earnings - End of year $</t>
+          <t>Property investigations</t>
         </is>
       </c>
       <c r="D480" t="inlineStr"/>
@@ -58918,16 +58690,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H480" s="5" t="n">
-        <v>4791.939</v>
-      </c>
-      <c r="I480" s="5" t="n">
-        <v>3647.093</v>
-      </c>
-      <c r="J480" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J480" s="5" t="n">
+        <v>0.178508</v>
       </c>
       <c r="K480" t="inlineStr">
         <is>
@@ -58998,19 +58772,15 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Earnings per share - Basic (Note 15) $</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Write-down of mineral properties (Note 8(a))</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -59026,16 +58796,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H481" s="5" t="n">
-        <v>1.2e-07</v>
-      </c>
-      <c r="I481" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J481" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J481" s="5" t="n">
+        <v>2.583765</v>
       </c>
       <c r="K481" t="inlineStr">
         <is>
@@ -59111,7 +58883,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>- Diluted (Note 15) $</t>
+          <t>Gain (loss) on sale of available-for-sale investments (Note 8(b))</t>
         </is>
       </c>
       <c r="D482" t="inlineStr"/>
@@ -59130,21 +58902,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H482" s="5" t="n">
-        <v>0.00011</v>
-      </c>
-      <c r="I482" s="5" t="n">
-        <v>-2e-05</v>
-      </c>
-      <c r="J482" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K482" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J482" s="5" t="n">
+        <v>-0.803305</v>
+      </c>
+      <c r="K482" s="5" t="n">
+        <v>0.237471</v>
       </c>
       <c r="L482" t="inlineStr">
         <is>
@@ -59215,12 +58987,12 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding - Basic</t>
+          <t>Current income tax expense</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -59233,26 +59005,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G483" s="5" t="n">
+        <v>-1.555409</v>
       </c>
       <c r="H483" s="5" t="n">
-        <v>65.159606</v>
-      </c>
-      <c r="I483" s="5" t="n">
-        <v>68.061035</v>
-      </c>
-      <c r="J483" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K483" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3531.865</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J483" s="5" t="n">
+        <v>0.050663</v>
+      </c>
+      <c r="K483" s="5" t="n">
+        <v>0.074002</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -59323,10 +59091,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding - Diluted</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr"/>
+          <t>Deferred income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -59342,21 +59114,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H484" s="5" t="n">
-        <v>66761.00599999999</v>
-      </c>
-      <c r="I484" s="5" t="n">
-        <v>69072.63</v>
-      </c>
-      <c r="J484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J484" s="5" t="n">
+        <v>1.577243</v>
+      </c>
+      <c r="K484" s="5" t="n">
+        <v>-1.217391</v>
       </c>
       <c r="L484" t="inlineStr">
         <is>
@@ -59422,17 +59194,17 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>and Retained Earnings</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Revenues $</t>
+          <t>Loss per share – Basic (Note 16(c)) $</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -59445,26 +59217,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G485" s="5" t="n">
-        <v>16.67771</v>
-      </c>
-      <c r="H485" s="5" t="n">
-        <v>24.26674</v>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J485" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="K485" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="L485" t="inlineStr">
         <is>
@@ -59530,19 +59302,15 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Operating expenses (Note 20)</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>– Diluted (Note 16(c)) $</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
           <t>-</t>
@@ -59553,26 +59321,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G486" s="5" t="n">
-        <v>8.210039999999999</v>
-      </c>
-      <c r="H486" s="5" t="n">
-        <v>10.125634</v>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I486" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J486" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="K486" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="L486" t="inlineStr">
         <is>
@@ -59638,15 +59406,19 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Business development investigations</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr"/>
+          <t>Mine operating earnings</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
@@ -59658,22 +59430,16 @@
         </is>
       </c>
       <c r="G487" s="5" t="n">
-        <v>0.082582</v>
-      </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.435484</v>
+      </c>
+      <c r="H487" s="5" t="n">
+        <v>12897.344</v>
+      </c>
+      <c r="I487" s="5" t="n">
+        <v>4035.981</v>
+      </c>
+      <c r="J487" s="5" t="n">
+        <v>515.812</v>
       </c>
       <c r="K487" t="inlineStr">
         <is>
@@ -59749,14 +59515,10 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Operating Income</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Ofﬁce, rent, insurance and sundry</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -59767,21 +59529,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G488" s="5" t="n">
-        <v>5.625958</v>
-      </c>
-      <c r="H488" s="5" t="n">
-        <v>10.471621</v>
-      </c>
-      <c r="I488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I488" s="5" t="n">
+        <v>513.9299999999999</v>
+      </c>
+      <c r="J488" s="5" t="n">
+        <v>340.789</v>
       </c>
       <c r="K488" t="inlineStr">
         <is>
@@ -59852,19 +59614,15 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Earnings before taxes</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Ofﬁce salaries and services</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -59875,21 +59633,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G489" s="5" t="n">
-        <v>5.470779</v>
-      </c>
-      <c r="H489" s="5" t="n">
-        <v>11.72549</v>
-      </c>
-      <c r="I489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I489" s="5" t="n">
+        <v>890.379</v>
+      </c>
+      <c r="J489" s="5" t="n">
+        <v>880.22</v>
       </c>
       <c r="K489" t="inlineStr">
         <is>
@@ -59960,12 +59718,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Retained Earnings (Deficit)- Beginning of year</t>
+          <t>Write-down of inventory (Note 6)</t>
         </is>
       </c>
       <c r="D490" t="inlineStr"/>
@@ -59979,21 +59737,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G490" s="5" t="n">
-        <v>-6.21852</v>
-      </c>
-      <c r="H490" s="5" t="n">
-        <v>-2.784351</v>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I490" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J490" s="5" t="n">
+        <v>359.896</v>
       </c>
       <c r="K490" t="inlineStr">
         <is>
@@ -60064,12 +59824,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Retained Earnings (Deficit) – End of year $</t>
+          <t>Write-down of mineral properties (Note 8 (a))</t>
         </is>
       </c>
       <c r="D491" t="inlineStr"/>
@@ -60083,21 +59843,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G491" s="5" t="n">
-        <v>-2.784351</v>
-      </c>
-      <c r="H491" s="5" t="n">
-        <v>4.791939</v>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I491" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J491" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J491" s="5" t="n">
+        <v>2583.765</v>
       </c>
       <c r="K491" t="inlineStr">
         <is>
@@ -60173,14 +59935,10 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Earnings per share – Basic (Note 11) $</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Write-down of available-for-sale investment (Note 8 (b))</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -60191,21 +59949,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G492" s="5" t="n">
-        <v>7e-08</v>
-      </c>
-      <c r="H492" s="5" t="n">
-        <v>1.2e-07</v>
-      </c>
-      <c r="I492" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J492" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I492" s="5" t="n">
+        <v>-750</v>
+      </c>
+      <c r="J492" s="5" t="n">
+        <v>-803.3049999999999</v>
       </c>
       <c r="K492" t="inlineStr">
         <is>
@@ -60281,92 +60039,2420 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
+          <t>Deferred income tax expense</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G493" s="5" t="n">
+        <v>-0.481201</v>
+      </c>
+      <c r="H493" s="5" t="n">
+        <v>-617.335</v>
+      </c>
+      <c r="I493" s="5" t="n">
+        <v>1104.009</v>
+      </c>
+      <c r="J493" s="5" t="n">
+        <v>1577.243</v>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Loss per share – Basic (Note 16 (c)) $</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I494" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J494" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>– Diluted (Note 16 (c)) $</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr"/>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I495" s="5" t="n">
+        <v>-2e-05</v>
+      </c>
+      <c r="J495" s="5" t="n">
+        <v>-0.00013</v>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Accounting audit and legal</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr"/>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H496" s="5" t="n">
+        <v>225.566</v>
+      </c>
+      <c r="I496" s="5" t="n">
+        <v>228.47</v>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G497" s="5" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="H497" s="5" t="n">
+        <v>211.575</v>
+      </c>
+      <c r="I497" s="5" t="n">
+        <v>223.159</v>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Write-down of available for sale investment (Note 20)</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr"/>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I498" s="5" t="n">
+        <v>-750</v>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Earnings (loss) before taxes</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr"/>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H499" s="5" t="n">
+        <v>11725.49</v>
+      </c>
+      <c r="I499" s="5" t="n">
+        <v>-40.837</v>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Net earnings</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G500" s="5" t="n">
+        <v>3.434169</v>
+      </c>
+      <c r="H500" s="5" t="n">
+        <v>7576.29</v>
+      </c>
+      <c r="I500" s="5" t="n">
+        <v>-1144.846</v>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Retained Earnings (Deficit) - Beginning of year</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H501" s="5" t="n">
+        <v>-2784.351</v>
+      </c>
+      <c r="I501" s="5" t="n">
+        <v>4791.939</v>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Retained earnings - End of year $</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr"/>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H502" s="5" t="n">
+        <v>4791.939</v>
+      </c>
+      <c r="I502" s="5" t="n">
+        <v>3647.093</v>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Earnings per share - Basic (Note 15) $</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H503" s="5" t="n">
+        <v>1.2e-07</v>
+      </c>
+      <c r="I503" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>- Diluted (Note 15) $</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H504" s="5" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="I504" s="5" t="n">
+        <v>-2e-05</v>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding - Basic</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H505" s="5" t="n">
+        <v>65.159606</v>
+      </c>
+      <c r="I505" s="5" t="n">
+        <v>68.061035</v>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding - Diluted</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H506" s="5" t="n">
+        <v>66761.00599999999</v>
+      </c>
+      <c r="I506" s="5" t="n">
+        <v>69072.63</v>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>and Retained Earnings</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Revenues $</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G507" s="5" t="n">
+        <v>16.67771</v>
+      </c>
+      <c r="H507" s="5" t="n">
+        <v>24.26674</v>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Operating expenses (Note 20)</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G508" s="5" t="n">
+        <v>8.210039999999999</v>
+      </c>
+      <c r="H508" s="5" t="n">
+        <v>10.125634</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Business development investigations</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr"/>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G509" s="5" t="n">
+        <v>0.082582</v>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G510" s="5" t="n">
+        <v>5.625958</v>
+      </c>
+      <c r="H510" s="5" t="n">
+        <v>10.471621</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Earnings before taxes</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G511" s="5" t="n">
+        <v>5.470779</v>
+      </c>
+      <c r="H511" s="5" t="n">
+        <v>11.72549</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Retained Earnings (Deficit)- Beginning of year</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr"/>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G512" s="5" t="n">
+        <v>-6.21852</v>
+      </c>
+      <c r="H512" s="5" t="n">
+        <v>-2.784351</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Retained Earnings (Deficit) – End of year $</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G513" s="5" t="n">
+        <v>-2.784351</v>
+      </c>
+      <c r="H513" s="5" t="n">
+        <v>4.791939</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Earnings per share – Basic (Note 11) $</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G514" s="5" t="n">
+        <v>7e-08</v>
+      </c>
+      <c r="H514" s="5" t="n">
+        <v>1.2e-07</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
           <t>– Diluted (Note 11) $</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
-      <c r="E493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G493" s="5" t="n">
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G515" s="5" t="n">
         <v>7e-08</v>
       </c>
-      <c r="H493" s="5" t="n">
+      <c r="H515" s="5" t="n">
         <v>1.1e-07</v>
       </c>
-      <c r="I493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V493" t="inlineStr">
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V515" t="inlineStr">
         <is>
           <t>-</t>
         </is>
